--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="931">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2815,6 +2815,12 @@
   </si>
   <si>
     <t>/Observation/GeneratePdf</t>
+  </si>
+  <si>
+    <t>GeneratePdf</t>
+  </si>
+  <si>
+    <t>/FieldAuditReport/GeneratePdf</t>
   </si>
 </sst>
 </file>
@@ -3149,7 +3155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K302"/>
+  <dimension ref="A1:K303"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13143,6 +13149,38 @@
         <v>927</v>
       </c>
     </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A303" s="1">
+        <v>393</v>
+      </c>
+      <c r="B303" s="1">
+        <v>393</v>
+      </c>
+      <c r="C303" s="1">
+        <v>8</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F303" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="G303" s="1">
+        <v>999</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I303" s="1">
+        <v>0</v>
+      </c>
+      <c r="K303" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:L305">
     <sortCondition ref="F2:F305"/>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="946">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2821,6 +2821,51 @@
   </si>
   <si>
     <t>/FieldAuditReport/GeneratePdf</t>
+  </si>
+  <si>
+    <t>Management Finalize Report</t>
+  </si>
+  <si>
+    <t>MANReport/Finalize</t>
+  </si>
+  <si>
+    <t>Finalize</t>
+  </si>
+  <si>
+    <t>StaffSnapshot</t>
+  </si>
+  <si>
+    <t>MANReport/StaffSnapshot</t>
+  </si>
+  <si>
+    <t>ParasSettledDuringAudit</t>
+  </si>
+  <si>
+    <t>MANReport/ParasSettledDuringAudit</t>
+  </si>
+  <si>
+    <t>ExecutiveSummary</t>
+  </si>
+  <si>
+    <t>MANReport/ExecutiveSummary</t>
+  </si>
+  <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>MANReport/Cover</t>
+  </si>
+  <si>
+    <t>AuditObservations</t>
+  </si>
+  <si>
+    <t>MANReport/AuditObservations</t>
+  </si>
+  <si>
+    <t>AuditObjectiveScope</t>
+  </si>
+  <si>
+    <t>MANReport/AuditObjectiveScope</t>
   </si>
 </sst>
 </file>
@@ -3155,7 +3200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K303"/>
+  <dimension ref="A1:K310"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13181,6 +13226,230 @@
         <v>929</v>
       </c>
     </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A304" s="1">
+        <v>400</v>
+      </c>
+      <c r="B304" s="1">
+        <v>400</v>
+      </c>
+      <c r="C304" s="1">
+        <v>8</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F304" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="G304" s="1">
+        <v>15</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I304" s="1">
+        <v>0</v>
+      </c>
+      <c r="K304" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>401</v>
+      </c>
+      <c r="B305" s="1">
+        <v>401</v>
+      </c>
+      <c r="C305" s="1">
+        <v>8</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F305" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="G305" s="1">
+        <v>12</v>
+      </c>
+      <c r="H305" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I305" s="1">
+        <v>0</v>
+      </c>
+      <c r="K305" s="1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A306" s="1">
+        <v>402</v>
+      </c>
+      <c r="B306" s="1">
+        <v>402</v>
+      </c>
+      <c r="C306" s="1">
+        <v>8</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F306" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="G306" s="1">
+        <v>14</v>
+      </c>
+      <c r="H306" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I306" s="1">
+        <v>0</v>
+      </c>
+      <c r="K306" s="1" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A307" s="1">
+        <v>403</v>
+      </c>
+      <c r="B307" s="1">
+        <v>403</v>
+      </c>
+      <c r="C307" s="1">
+        <v>8</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F307" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="G307" s="1">
+        <v>13</v>
+      </c>
+      <c r="H307" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I307" s="1">
+        <v>0</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A308" s="1">
+        <v>404</v>
+      </c>
+      <c r="B308" s="1">
+        <v>404</v>
+      </c>
+      <c r="C308" s="1">
+        <v>8</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F308" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="G308" s="1">
+        <v>9</v>
+      </c>
+      <c r="H308" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I308" s="1">
+        <v>0</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A309" s="1">
+        <v>405</v>
+      </c>
+      <c r="B309" s="1">
+        <v>405</v>
+      </c>
+      <c r="C309" s="1">
+        <v>8</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F309" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="G309" s="1">
+        <v>16</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I309" s="1">
+        <v>0</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>406</v>
+      </c>
+      <c r="B310" s="1">
+        <v>406</v>
+      </c>
+      <c r="C310" s="1">
+        <v>8</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F310" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="G310" s="1">
+        <v>11</v>
+      </c>
+      <c r="H310" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I310" s="1">
+        <v>0</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:L305">
     <sortCondition ref="F2:F305"/>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="957">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2866,6 +2866,39 @@
   </si>
   <si>
     <t>MANReport/AuditObjectiveScope</t>
+  </si>
+  <si>
+    <t>FFR PART 1</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART1</t>
+  </si>
+  <si>
+    <t>FFR_PART1</t>
+  </si>
+  <si>
+    <t>FFR PART 2</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART2</t>
+  </si>
+  <si>
+    <t>FFR_PART2</t>
+  </si>
+  <si>
+    <t>FFR PART 3</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART3</t>
+  </si>
+  <si>
+    <t>FFR_PART3</t>
+  </si>
+  <si>
+    <t>TaskListIID</t>
+  </si>
+  <si>
+    <t>IID/TaskListIID</t>
   </si>
 </sst>
 </file>
@@ -3200,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K310"/>
+  <dimension ref="A1:K314"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13450,6 +13483,138 @@
         <v>944</v>
       </c>
     </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A311" s="1">
+        <f>B311</f>
+        <v>407</v>
+      </c>
+      <c r="B311" s="1">
+        <v>407</v>
+      </c>
+      <c r="C311" s="1">
+        <v>7</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F311" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="G311" s="1">
+        <v>1</v>
+      </c>
+      <c r="H311" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I311" s="1">
+        <v>0</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <f>B312</f>
+        <v>408</v>
+      </c>
+      <c r="B312" s="1">
+        <v>408</v>
+      </c>
+      <c r="C312" s="1">
+        <v>7</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F312" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="G312" s="1">
+        <v>2</v>
+      </c>
+      <c r="H312" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I312" s="1">
+        <v>0</v>
+      </c>
+      <c r="K312" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A313" s="1">
+        <f>B313</f>
+        <v>408</v>
+      </c>
+      <c r="B313" s="1">
+        <v>408</v>
+      </c>
+      <c r="C313" s="1">
+        <v>7</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F313" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="G313" s="1">
+        <v>3</v>
+      </c>
+      <c r="H313" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I313" s="1">
+        <v>0</v>
+      </c>
+      <c r="K313" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <f>B314</f>
+        <v>409</v>
+      </c>
+      <c r="B314" s="1">
+        <v>409</v>
+      </c>
+      <c r="C314" s="1">
+        <v>7</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F314" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="G314" s="1">
+        <v>13</v>
+      </c>
+      <c r="H314" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I314" s="1">
+        <v>0</v>
+      </c>
+      <c r="K314" s="1" t="s">
+        <v>955</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:L305">
     <sortCondition ref="F2:F305"/>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAS\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="952">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2868,37 +2868,22 @@
     <t>MANReport/AuditObjectiveScope</t>
   </si>
   <si>
-    <t>FFR PART 1</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART1</t>
-  </si>
-  <si>
-    <t>FFR_PART1</t>
-  </si>
-  <si>
-    <t>FFR PART 2</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART2</t>
-  </si>
-  <si>
-    <t>FFR_PART2</t>
-  </si>
-  <si>
-    <t>FFR PART 3</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART3</t>
-  </si>
-  <si>
-    <t>FFR_PART3</t>
-  </si>
-  <si>
     <t>TaskListIID</t>
   </si>
   <si>
     <t>IID/TaskListIID</t>
+  </si>
+  <si>
+    <t>Inquiry Report PDF</t>
+  </si>
+  <si>
+    <t>Monitoring Dashboard</t>
+  </si>
+  <si>
+    <t>IID/InquiryReportReadOnly</t>
+  </si>
+  <si>
+    <t>IID/MonitoringDashboard</t>
   </si>
 </sst>
 </file>
@@ -3233,7 +3218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K313"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13486,22 +13471,22 @@
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <f>B311</f>
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B311" s="1">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C311" s="1">
         <v>7</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G311" s="1">
         <v>1</v>
@@ -13519,10 +13504,10 @@
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <f>B312</f>
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B312" s="1">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C312" s="1">
         <v>7</v>
@@ -13534,7 +13519,7 @@
         <v>886</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G312" s="1">
         <v>2</v>
@@ -13546,31 +13531,31 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <f>B313</f>
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B313" s="1">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C313" s="1">
         <v>7</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="G313" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H313" s="1" t="s">
         <v>770</v>
@@ -13579,40 +13564,7 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A314" s="1">
-        <f>B314</f>
-        <v>409</v>
-      </c>
-      <c r="B314" s="1">
-        <v>409</v>
-      </c>
-      <c r="C314" s="1">
-        <v>7</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="F314" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="G314" s="1">
-        <v>13</v>
-      </c>
-      <c r="H314" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I314" s="1">
-        <v>0</v>
-      </c>
-      <c r="K314" s="1" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAS\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="957">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2868,22 +2868,37 @@
     <t>MANReport/AuditObjectiveScope</t>
   </si>
   <si>
+    <t>FFR PART 1</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART1</t>
+  </si>
+  <si>
+    <t>FFR_PART1</t>
+  </si>
+  <si>
+    <t>FFR PART 2</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART2</t>
+  </si>
+  <si>
+    <t>FFR_PART2</t>
+  </si>
+  <si>
+    <t>FFR PART 3</t>
+  </si>
+  <si>
+    <t>IID/FFR_PART3</t>
+  </si>
+  <si>
+    <t>FFR_PART3</t>
+  </si>
+  <si>
     <t>TaskListIID</t>
   </si>
   <si>
     <t>IID/TaskListIID</t>
-  </si>
-  <si>
-    <t>Inquiry Report PDF</t>
-  </si>
-  <si>
-    <t>Monitoring Dashboard</t>
-  </si>
-  <si>
-    <t>IID/InquiryReportReadOnly</t>
-  </si>
-  <si>
-    <t>IID/MonitoringDashboard</t>
   </si>
 </sst>
 </file>
@@ -3218,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K313"/>
+  <dimension ref="A1:K314"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13471,22 +13486,22 @@
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <f>B311</f>
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B311" s="1">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C311" s="1">
         <v>7</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="G311" s="1">
         <v>1</v>
@@ -13504,10 +13519,10 @@
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <f>B312</f>
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B312" s="1">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C312" s="1">
         <v>7</v>
@@ -13519,7 +13534,7 @@
         <v>886</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G312" s="1">
         <v>2</v>
@@ -13531,40 +13546,73 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <f>B313</f>
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B313" s="1">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C313" s="1">
         <v>7</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="G313" s="1">
+        <v>3</v>
+      </c>
+      <c r="H313" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I313" s="1">
+        <v>0</v>
+      </c>
+      <c r="K313" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A314" s="1">
+        <f>B314</f>
+        <v>409</v>
+      </c>
+      <c r="B314" s="1">
+        <v>409</v>
+      </c>
+      <c r="C314" s="1">
+        <v>7</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F314" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="G314" s="1">
         <v>13</v>
       </c>
-      <c r="H313" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I313" s="1">
-        <v>0</v>
-      </c>
-      <c r="K313" s="1" t="s">
-        <v>946</v>
+      <c r="H314" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I314" s="1">
+        <v>0</v>
+      </c>
+      <c r="K314" s="1" t="s">
+        <v>955</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="965">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2868,37 +2868,61 @@
     <t>MANReport/AuditObjectiveScope</t>
   </si>
   <si>
-    <t>FFR PART 1</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART1</t>
-  </si>
-  <si>
-    <t>FFR_PART1</t>
-  </si>
-  <si>
-    <t>FFR PART 2</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART2</t>
-  </si>
-  <si>
-    <t>FFR_PART2</t>
-  </si>
-  <si>
-    <t>FFR PART 3</t>
-  </si>
-  <si>
-    <t>IID/FFR_PART3</t>
-  </si>
-  <si>
-    <t>FFR_PART3</t>
-  </si>
-  <si>
     <t>TaskListIID</t>
   </si>
   <si>
     <t>IID/TaskListIID</t>
+  </si>
+  <si>
+    <t>Planning Dash Board</t>
+  </si>
+  <si>
+    <t>Planning/Planning</t>
+  </si>
+  <si>
+    <t>Field Audit Dashboard</t>
+  </si>
+  <si>
+    <t>FieldAudit/AR_Dashboard</t>
+  </si>
+  <si>
+    <t>AR_Dashboard</t>
+  </si>
+  <si>
+    <t>FieldAudit/BO_Dashboard</t>
+  </si>
+  <si>
+    <t>BO_Dashboard</t>
+  </si>
+  <si>
+    <t>IID/MonitoringDashboard</t>
+  </si>
+  <si>
+    <t>IID Monitoring Dashboard</t>
+  </si>
+  <si>
+    <t>MonitoringDashboard</t>
+  </si>
+  <si>
+    <t>InquiryReportReadOnly</t>
+  </si>
+  <si>
+    <t>Inquiry Report ReadOnly</t>
+  </si>
+  <si>
+    <t>IID/InquiryReportReadOnly</t>
+  </si>
+  <si>
+    <t>FieldAuditReport/Engagements</t>
+  </si>
+  <si>
+    <t>Engagements</t>
+  </si>
+  <si>
+    <t>ObservationPdf/ObservationPrint</t>
+  </si>
+  <si>
+    <t>ObservationPrint</t>
   </si>
 </sst>
 </file>
@@ -2949,10 +2973,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3233,7 +3259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K318"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13495,13 +13521,13 @@
         <v>7</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="G311" s="1">
         <v>1</v>
@@ -13513,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
@@ -13528,13 +13554,13 @@
         <v>7</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="G312" s="1">
         <v>2</v>
@@ -13546,28 +13572,28 @@
         <v>0</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <f>B313</f>
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B313" s="1">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C313" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="G313" s="1">
         <v>3</v>
@@ -13579,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
@@ -13594,13 +13620,13 @@
         <v>7</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>886</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="G314" s="1">
         <v>13</v>
@@ -13612,7 +13638,142 @@
         <v>0</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>955</v>
+        <v>946</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A315" s="4">
+        <f t="shared" ref="A315:A318" si="5">B315</f>
+        <v>410</v>
+      </c>
+      <c r="B315" s="4">
+        <v>410</v>
+      </c>
+      <c r="C315" s="4">
+        <v>3</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="G315" s="4">
+        <v>1</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I315" s="4">
+        <v>0</v>
+      </c>
+      <c r="J315" s="3"/>
+      <c r="K315" s="4" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A316" s="4">
+        <f t="shared" si="5"/>
+        <v>411</v>
+      </c>
+      <c r="B316" s="4">
+        <v>411</v>
+      </c>
+      <c r="C316" s="4">
+        <v>8</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="G316" s="4">
+        <v>1</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I316" s="4">
+        <v>0</v>
+      </c>
+      <c r="J316" s="4"/>
+      <c r="K316" s="4" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A317" s="4">
+        <f t="shared" si="5"/>
+        <v>412</v>
+      </c>
+      <c r="B317" s="4">
+        <v>412</v>
+      </c>
+      <c r="C317" s="4">
+        <v>8</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="G317" s="4">
+        <v>1</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I317" s="4">
+        <v>0</v>
+      </c>
+      <c r="J317" s="4"/>
+      <c r="K317" s="4" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A318" s="4">
+        <f t="shared" si="5"/>
+        <v>398</v>
+      </c>
+      <c r="B318" s="1">
+        <v>398</v>
+      </c>
+      <c r="C318" s="1">
+        <v>8</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="F318" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="G318" s="4">
+        <v>1</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I318" s="4">
+        <v>0</v>
+      </c>
+      <c r="K318" s="1" t="s">
+        <v>964</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAS\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="968">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2923,6 +2923,15 @@
   </si>
   <si>
     <t>ObservationPrint</t>
+  </si>
+  <si>
+    <t>MA_Dashboard</t>
+  </si>
+  <si>
+    <t>ManagementAudit/MA_Dashboard</t>
+  </si>
+  <si>
+    <t>Management Audit Dashboard</t>
   </si>
 </sst>
 </file>
@@ -3259,7 +3268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K318"/>
+  <dimension ref="A1:K319"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13643,7 +13652,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A318" si="5">B315</f>
+        <f t="shared" ref="A315:A319" si="5">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -13774,6 +13783,39 @@
       </c>
       <c r="K318" s="1" t="s">
         <v>964</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A319" s="1">
+        <f t="shared" si="5"/>
+        <v>413</v>
+      </c>
+      <c r="B319" s="1">
+        <v>413</v>
+      </c>
+      <c r="C319" s="1">
+        <v>8</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="G319" s="1">
+        <v>1</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I319" s="4">
+        <v>0</v>
+      </c>
+      <c r="K319" s="4" t="s">
+        <v>965</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="977">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2932,6 +2932,33 @@
   </si>
   <si>
     <t>Management Audit Dashboard</t>
+  </si>
+  <si>
+    <t>Entity Dashboard</t>
+  </si>
+  <si>
+    <t>AdministrationPanel/Entity_Dashboard</t>
+  </si>
+  <si>
+    <t>Entity_Dashboard</t>
+  </si>
+  <si>
+    <t>User Dashboard</t>
+  </si>
+  <si>
+    <t>AdministrationPanel/User_Dashboard</t>
+  </si>
+  <si>
+    <t>User_Dashboard</t>
+  </si>
+  <si>
+    <t>Checklist Dashboard</t>
+  </si>
+  <si>
+    <t>Setup/Checklist_Dashboard</t>
+  </si>
+  <si>
+    <t>Checklist_Dashboard</t>
   </si>
 </sst>
 </file>
@@ -3268,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K319"/>
+  <dimension ref="A1:K322"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -13652,7 +13679,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A319" si="5">B315</f>
+        <f t="shared" ref="A315:A322" si="5">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -13816,6 +13843,105 @@
       </c>
       <c r="K319" s="4" t="s">
         <v>965</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A320" s="4">
+        <f t="shared" si="5"/>
+        <v>414</v>
+      </c>
+      <c r="B320" s="1">
+        <v>414</v>
+      </c>
+      <c r="C320" s="1">
+        <v>10</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="G320" s="1">
+        <v>1</v>
+      </c>
+      <c r="H320" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I320" s="1">
+        <v>0</v>
+      </c>
+      <c r="K320" s="1" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A321" s="4">
+        <f t="shared" si="5"/>
+        <v>415</v>
+      </c>
+      <c r="B321" s="1">
+        <v>415</v>
+      </c>
+      <c r="C321" s="1">
+        <v>10</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="F321" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="G321" s="1">
+        <v>1</v>
+      </c>
+      <c r="H321" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I321" s="1">
+        <v>0</v>
+      </c>
+      <c r="K321" s="1" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A322" s="4">
+        <f t="shared" si="5"/>
+        <v>416</v>
+      </c>
+      <c r="B322" s="1">
+        <v>416</v>
+      </c>
+      <c r="C322" s="1">
+        <v>6</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="G322" s="1">
+        <v>1</v>
+      </c>
+      <c r="H322" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I322" s="1">
+        <v>0</v>
+      </c>
+      <c r="K322" s="1" t="s">
+        <v>976</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -1,33 +1,346 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$299</definedName>
-  </definedNames>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>2</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="2" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+      <vt:lpstr>Sheet2</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>AAA</dc:creator>
+  <cp:lastModifiedBy>Asad Ali Chaudhry</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2025-08-09T21:54:51Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-27T05:54:50Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
+<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <c r="A322" i="1" l="1"/>
+  <c r="A321" i="1"/>
+  <c r="A320" i="1"/>
+  <c r="A319" i="1" l="1"/>
+  <c r="A315" i="1" l="1"/>
+  <c r="A316" i="1"/>
+  <c r="A317" i="1"/>
+  <c r="A318" i="1"/>
+  <c r="A314" i="1" l="1"/>
+  <c r="A313" i="1" l="1"/>
+  <c r="A312" i="1"/>
+  <c r="A311" i="1"/>
+  <c r="A142" i="1" l="1"/>
+  <c r="A150" i="1"/>
+  <c r="A143" i="1"/>
+  <c r="A157" i="1"/>
+  <c r="A148" i="1"/>
+  <c r="A149" i="1"/>
+  <c r="A156" i="1"/>
+  <c r="A158" i="1"/>
+  <c r="A61" i="1"/>
+  <c r="A60" i="1"/>
+  <c r="A62" i="1"/>
+  <c r="A66" i="1"/>
+  <c r="A65" i="1"/>
+  <c r="A58" i="1"/>
+  <c r="A175" i="1"/>
+  <c r="A233" i="1"/>
+  <c r="A227" i="1"/>
+  <c r="A188" i="1"/>
+  <c r="A231" i="1"/>
+  <c r="A225" i="1"/>
+  <c r="A171" i="1"/>
+  <c r="A267" i="1"/>
+  <c r="A275" i="1"/>
+  <c r="A280" i="1"/>
+  <c r="A274" i="1"/>
+  <c r="A273" i="1"/>
+  <c r="A144" i="1"/>
+  <c r="A145" i="1"/>
+  <c r="A22" i="1"/>
+  <c r="A21" i="1"/>
+  <c r="A14" i="1"/>
+  <c r="A5" i="1"/>
+  <c r="A4" i="1"/>
+  <c r="A28" i="1"/>
+  <c r="A153" i="1"/>
+  <c r="A31" i="1"/>
+  <c r="A17" i="1"/>
+  <c r="A30" i="1"/>
+  <c r="A29" i="1"/>
+  <c r="A50" i="1"/>
+  <c r="A13" i="1"/>
+  <c r="A12" i="1"/>
+  <c r="A18" i="1"/>
+  <c r="A19" i="1"/>
+  <c r="A64" i="1"/>
+  <c r="A155" i="1"/>
+  <c r="A241" i="1"/>
+  <c r="A57" i="1"/>
+  <c r="A245" i="1"/>
+  <c r="A154" i="1"/>
+  <c r="A240" i="1"/>
+  <c r="A146" i="1"/>
+  <c r="A244" i="1"/>
+  <c r="A147" i="1"/>
+  <c r="A53" i="1"/>
+  <c r="A56" i="1"/>
+  <c r="A59" i="1"/>
+  <c r="A55" i="1"/>
+  <c r="A54" i="1"/>
+  <c r="A75" i="1"/>
+  <c r="A106" i="1"/>
+  <c r="A76" i="1"/>
+  <c r="A99" i="1"/>
+  <c r="A96" i="1"/>
+  <c r="A100" i="1"/>
+  <c r="A212" i="1"/>
+  <c r="A217" i="1"/>
+  <c r="A84" i="1"/>
+  <c r="A78" i="1"/>
+  <c r="A211" i="1"/>
+  <c r="A93" i="1"/>
+  <c r="A87" i="1"/>
+  <c r="A73" i="1"/>
+  <c r="A83" i="1"/>
+  <c r="A34" i="1"/>
+  <c r="A35" i="1"/>
+  <c r="A32" i="1"/>
+  <c r="A179" i="1"/>
+  <c r="A219" i="1"/>
+  <c r="A192" i="1"/>
+  <c r="A181" i="1"/>
+  <c r="A230" i="1"/>
+  <c r="A239" i="1"/>
+  <c r="A223" i="1"/>
+  <c r="A221" i="1"/>
+  <c r="A173" i="1"/>
+  <c r="A190" i="1"/>
+  <c r="A191" i="1"/>
+  <c r="A182" i="1"/>
+  <c r="A218" i="1"/>
+  <c r="A194" i="1"/>
+  <c r="A180" i="1"/>
+  <c r="A235" i="1"/>
+  <c r="A238" i="1"/>
+  <c r="A126" i="1"/>
+  <c r="A97" i="1"/>
+  <c r="A105" i="1"/>
+  <c r="A88" i="1"/>
+  <c r="A42" i="1"/>
+  <c r="A74" i="1"/>
+  <c r="A213" i="1"/>
+  <c r="A178" i="1"/>
+  <c r="A214" i="1"/>
+  <c r="A81" i="1"/>
+  <c r="A82" i="1"/>
+  <c r="A79" i="1"/>
+  <c r="A89" i="1"/>
+  <c r="A90" i="1"/>
+  <c r="A209" i="1"/>
+  <c r="A186" i="1"/>
+  <c r="A187" i="1"/>
+  <c r="A94" i="1"/>
+  <c r="A85" i="1"/>
+  <c r="A95" i="1"/>
+  <c r="A67" i="1"/>
+  <c r="A68" i="1"/>
+  <c r="A183" i="1"/>
+  <c r="A128" i="1"/>
+  <c r="A129" i="1"/>
+  <c r="A104" i="1"/>
+  <c r="A177" i="1"/>
+  <c r="A71" i="1"/>
+  <c r="A237" i="1"/>
+  <c r="A206" i="1"/>
+  <c r="A201" i="1"/>
+  <c r="A195" i="1"/>
+  <c r="A196" i="1"/>
+  <c r="A172" i="1"/>
+  <c r="A200" i="1"/>
+  <c r="A198" i="1"/>
+  <c r="A197" i="1"/>
+  <c r="A199" i="1"/>
+  <c r="A101" i="1"/>
+  <c r="A122" i="1"/>
+  <c r="A108" i="1"/>
+  <c r="A203" i="1"/>
+  <c r="A208" i="1"/>
+  <c r="A207" i="1"/>
+  <c r="A109" i="1"/>
+  <c r="A204" i="1"/>
+  <c r="A205" i="1"/>
+  <c r="A25" i="1"/>
+  <c r="A63" i="1"/>
+  <c r="A70" i="1"/>
+  <c r="A107" i="1"/>
+  <c r="A72" i="1"/>
+  <c r="A202" i="1"/>
+  <c r="A110" i="1"/>
+  <c r="A39" i="1"/>
+  <c r="A49" i="1"/>
+  <c r="A44" i="1"/>
+  <c r="A45" i="1"/>
+  <c r="A37" i="1"/>
+  <c r="A272" i="1"/>
+  <c r="A270" i="1"/>
+  <c r="A224" i="1"/>
+  <c r="A20" i="1"/>
+  <c r="A6" i="1"/>
+  <c r="A269" i="1"/>
+  <c r="A276" i="1"/>
+  <c r="A281" i="1"/>
+  <c r="A24" i="1"/>
+  <c r="A10" i="1"/>
+  <c r="A9" i="1"/>
+  <c r="A11" i="1"/>
+  <c r="A164" i="1"/>
+  <c r="A166" i="1"/>
+  <c r="A165" i="1"/>
+  <c r="A43" i="1"/>
+  <c r="A216" i="1"/>
+  <c r="A23" i="1"/>
+  <c r="A242" i="1"/>
+  <c r="A103" i="1"/>
+  <c r="A234" i="1"/>
+  <c r="A226" i="1"/>
+  <c r="A184" i="1"/>
+  <c r="A77" i="1"/>
+  <c r="A220" i="1"/>
+  <c r="A285" i="1"/>
+  <c r="A286" i="1"/>
+  <c r="A282" i="1"/>
+  <c r="A284" i="1"/>
+  <c r="A283" i="1"/>
+  <c r="A33" i="1"/>
+  <c r="A36" i="1"/>
+  <c r="A40" i="1"/>
+  <c r="A46" i="1"/>
+  <c r="A47" i="1"/>
+  <c r="A262" i="1"/>
+  <c r="A277" i="1"/>
+  <c r="A263" i="1"/>
+  <c r="A41" i="1"/>
+  <c r="A167" i="1"/>
+  <c r="A232" i="1"/>
+  <c r="A15" i="1"/>
+  <c r="A174" i="1"/>
+  <c r="A98" i="1"/>
+  <c r="A38" i="1"/>
+  <c r="A168" i="1"/>
+  <c r="A8" i="1"/>
+  <c r="A215" i="1"/>
+  <c r="A189" i="1"/>
+  <c r="A26" i="1"/>
+  <c r="A80" i="1"/>
+  <c r="A86" i="1"/>
+  <c r="A3" i="1"/>
+  <c r="A287" i="1"/>
+  <c r="A210" i="1"/>
+  <c r="A176" i="1"/>
+  <c r="A268" i="1"/>
+  <c r="A271" i="1"/>
+  <c r="A246" i="1"/>
+  <c r="A278" i="1"/>
+  <c r="A264" i="1"/>
+  <c r="A279" i="1"/>
+  <c r="A265" i="1"/>
+  <c r="A185" i="1"/>
+  <c r="A266" i="1"/>
+  <c r="A16" i="1"/>
+  <c r="A229" i="1"/>
+  <c r="A169" i="1"/>
+  <c r="A170" i="1"/>
+  <c r="A193" i="1"/>
+  <c r="A161" i="1"/>
+  <c r="A160" i="1"/>
+  <c r="A159" i="1"/>
+  <c r="A151" i="1"/>
+  <c r="A152" i="1"/>
+  <c r="A91" i="1"/>
+  <c r="A92" i="1"/>
+  <c r="A69" i="1"/>
+  <c r="A48" i="1"/>
+  <c r="A102" i="1"/>
+  <c r="A255" i="1"/>
+  <c r="A247" i="1"/>
+  <c r="A252" i="1"/>
+  <c r="A250" i="1"/>
+  <c r="A249" i="1"/>
+  <c r="A258" i="1"/>
+  <c r="A236" i="1"/>
+  <c r="A228" i="1"/>
+  <c r="A257" i="1"/>
+  <c r="A256" i="1"/>
+  <c r="A261" i="1"/>
+  <c r="A222" i="1"/>
+  <c r="A248" i="1"/>
+  <c r="A251" i="1"/>
+  <c r="A254" i="1"/>
+  <c r="A116" i="1"/>
+  <c r="A259" i="1"/>
+  <c r="A117" i="1"/>
+  <c r="A2" i="1"/>
+  <c r="A123" i="1"/>
+  <c r="A27" i="1"/>
+  <c r="A7" i="1"/>
+  <c r="A115" i="1"/>
+  <c r="A133" i="1"/>
+  <c r="A132" i="1"/>
+  <c r="A134" i="1"/>
+  <c r="A135" i="1"/>
+  <c r="A136" i="1"/>
+  <c r="A137" i="1"/>
+  <c r="A138" i="1"/>
+  <c r="A139" i="1"/>
+  <c r="A140" i="1"/>
+  <c r="A141" i="1"/>
+  <c r="A162" i="1"/>
+  <c r="A163" i="1"/>
+  <c r="A51" i="1"/>
+  <c r="A52" i="1"/>
+  <c r="A114" i="1"/>
+  <c r="A111" i="1"/>
+  <c r="A119" i="1"/>
+  <c r="A120" i="1"/>
+  <c r="A121" i="1"/>
+  <c r="A124" i="1"/>
+  <c r="A118" i="1"/>
+  <c r="A125" i="1"/>
+  <c r="A113" i="1"/>
+  <c r="A112" i="1"/>
+  <c r="A130" i="1"/>
+  <c r="A131" i="1"/>
+  <c r="A127" i="1"/>
+  <c r="A260" i="1"/>
+  <c r="A253" i="1"/>
+  <c r="A243" i="1"/>
+</calcChain>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="977">
   <si>
     <t>PAGE_NAME</t>
@@ -2963,7 +3276,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -3032,7 +3345,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -3293,7 +3606,35 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$299</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K322"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
@@ -3413,72 +3754,6 @@
         <v>710</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B4" s="1">
-        <v>45</v>
-      </c>
-      <c r="C4" s="1">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G4" s="1">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B5" s="1">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G5" s="1">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
@@ -3611,39 +3886,6 @@
         <v>706</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>216</v>
-      </c>
-      <c r="B10" s="1">
-        <v>216</v>
-      </c>
-      <c r="C10" s="1">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="G10" s="1">
-        <v>7</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>705</v>
-      </c>
-    </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
@@ -3842,39 +4084,6 @@
         <v>711</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B17" s="1">
-        <v>50</v>
-      </c>
-      <c r="C17" s="1">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G17" s="1">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
@@ -4304,39 +4513,6 @@
         <v>692</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B31" s="1">
-        <v>48</v>
-      </c>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
@@ -4667,204 +4843,6 @@
         <v>728</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <f t="shared" si="0"/>
-        <v>125</v>
-      </c>
-      <c r="B42" s="1">
-        <v>125</v>
-      </c>
-      <c r="C42" s="1">
-        <v>16</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="G42" s="1">
-        <v>3</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <f t="shared" si="0"/>
-        <v>223</v>
-      </c>
-      <c r="B43" s="1">
-        <v>223</v>
-      </c>
-      <c r="C43" s="1">
-        <v>16</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="G43" s="1">
-        <v>5</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="B44" s="1">
-        <v>200</v>
-      </c>
-      <c r="C44" s="1">
-        <v>16</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G44" s="1">
-        <v>2</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <f t="shared" si="0"/>
-        <v>201</v>
-      </c>
-      <c r="B45" s="1">
-        <v>201</v>
-      </c>
-      <c r="C45" s="1">
-        <v>16</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="G45" s="1">
-        <v>3</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <f t="shared" si="0"/>
-        <v>243</v>
-      </c>
-      <c r="B46" s="1">
-        <v>243</v>
-      </c>
-      <c r="C46" s="1">
-        <v>16</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <f t="shared" si="0"/>
-        <v>244</v>
-      </c>
-      <c r="B47" s="1">
-        <v>244</v>
-      </c>
-      <c r="C47" s="1">
-        <v>16</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>722</v>
-      </c>
-    </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
@@ -5360,39 +5338,6 @@
         <v>527</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
-        <f t="shared" si="0"/>
-        <v>192</v>
-      </c>
-      <c r="B63" s="1">
-        <v>192</v>
-      </c>
-      <c r="C63" s="1">
-        <v>4</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G63" s="1">
-        <v>2</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I63" s="1">
-        <v>0</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
@@ -5426,39 +5371,6 @@
         <v>784</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
-        <f t="shared" ref="A65:A118" si="1">B65</f>
-        <v>18</v>
-      </c>
-      <c r="B65" s="1">
-        <v>18</v>
-      </c>
-      <c r="C65" s="1">
-        <v>4</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G65" s="1">
-        <v>4</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I65" s="1">
-        <v>1</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <f t="shared" si="1"/>
@@ -5591,138 +5503,6 @@
         <v>568</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <f t="shared" si="1"/>
-        <v>193</v>
-      </c>
-      <c r="B70" s="1">
-        <v>193</v>
-      </c>
-      <c r="C70" s="1">
-        <v>4</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G70" s="1">
-        <v>3</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
-        <f t="shared" si="1"/>
-        <v>169</v>
-      </c>
-      <c r="B71" s="1">
-        <v>169</v>
-      </c>
-      <c r="C71" s="1">
-        <v>19</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="G71" s="1">
-        <v>8</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I71" s="1">
-        <v>0</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
-        <f t="shared" si="1"/>
-        <v>195</v>
-      </c>
-      <c r="B72" s="1">
-        <v>195</v>
-      </c>
-      <c r="C72" s="1">
-        <v>4</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G72" s="1">
-        <v>5</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I72" s="1">
-        <v>0</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B73" s="1">
-        <v>88</v>
-      </c>
-      <c r="C73" s="1">
-        <v>4</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G73" s="1">
-        <v>21</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I73" s="1">
-        <v>1</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>539</v>
-      </c>
-    </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
@@ -5954,105 +5734,6 @@
         <v>570</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
-        <f t="shared" si="1"/>
-        <v>148</v>
-      </c>
-      <c r="B81" s="1">
-        <v>148</v>
-      </c>
-      <c r="C81" s="1">
-        <v>4</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G81" s="1">
-        <v>5</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="I81" s="1">
-        <v>1</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
-        <f t="shared" si="1"/>
-        <v>149</v>
-      </c>
-      <c r="B82" s="1">
-        <v>149</v>
-      </c>
-      <c r="C82" s="1">
-        <v>4</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G82" s="1">
-        <v>6</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I82" s="1">
-        <v>1</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B83" s="1">
-        <v>89</v>
-      </c>
-      <c r="C83" s="1">
-        <v>4</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G83" s="1">
-        <v>22</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I83" s="1">
-        <v>1</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
@@ -6152,138 +5833,6 @@
         <v>571</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B87" s="1">
-        <v>87</v>
-      </c>
-      <c r="C87" s="1">
-        <v>4</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G87" s="1">
-        <v>20</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I87" s="1">
-        <v>1</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
-        <f t="shared" si="1"/>
-        <v>124</v>
-      </c>
-      <c r="B88" s="1">
-        <v>124</v>
-      </c>
-      <c r="C88" s="1">
-        <v>4</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G88" s="1">
-        <v>6</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I88" s="1">
-        <v>1</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
-        <f t="shared" si="1"/>
-        <v>151</v>
-      </c>
-      <c r="B89" s="1">
-        <v>151</v>
-      </c>
-      <c r="C89" s="1">
-        <v>4</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G89" s="1">
-        <v>20</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I89" s="1">
-        <v>1</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
-        <f t="shared" si="1"/>
-        <v>152</v>
-      </c>
-      <c r="B90" s="1">
-        <v>152</v>
-      </c>
-      <c r="C90" s="1">
-        <v>4</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G90" s="1">
-        <v>21</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I90" s="1">
-        <v>1</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
@@ -6515,105 +6064,6 @@
         <v>542</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
-        <f t="shared" si="1"/>
-        <v>253</v>
-      </c>
-      <c r="B98" s="1">
-        <v>253</v>
-      </c>
-      <c r="C98" s="1">
-        <v>4</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G98" s="1">
-        <v>1</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I98" s="1">
-        <v>1</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B99" s="1">
-        <v>78</v>
-      </c>
-      <c r="C99" s="1">
-        <v>4</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G99" s="1">
-        <v>3</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I99" s="1">
-        <v>0</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="B100" s="1">
-        <v>80</v>
-      </c>
-      <c r="C100" s="1">
-        <v>4</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G100" s="1">
-        <v>9</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I100" s="1">
-        <v>0</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>536</v>
-      </c>
-    </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
@@ -6713,72 +6163,6 @@
         <v>564</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
-        <f t="shared" si="1"/>
-        <v>167</v>
-      </c>
-      <c r="B104" s="1">
-        <v>167</v>
-      </c>
-      <c r="C104" s="1">
-        <v>19</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="G104" s="1">
-        <v>7</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I104" s="1">
-        <v>0</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
-        <f t="shared" si="1"/>
-        <v>123</v>
-      </c>
-      <c r="B105" s="1">
-        <v>123</v>
-      </c>
-      <c r="C105" s="1">
-        <v>4</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G105" s="1">
-        <v>6</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I105" s="1">
-        <v>1</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
@@ -6812,138 +6196,6 @@
         <v>523</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
-        <f t="shared" si="1"/>
-        <v>194</v>
-      </c>
-      <c r="B107" s="1">
-        <v>194</v>
-      </c>
-      <c r="C107" s="1">
-        <v>4</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G107" s="1">
-        <v>4</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I107" s="1">
-        <v>0</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
-        <f t="shared" si="1"/>
-        <v>183</v>
-      </c>
-      <c r="B108" s="1">
-        <v>183</v>
-      </c>
-      <c r="C108" s="1">
-        <v>4</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G108" s="1">
-        <v>19</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I108" s="1">
-        <v>0</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
-      </c>
-      <c r="B109" s="1">
-        <v>188</v>
-      </c>
-      <c r="C109" s="1">
-        <v>4</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G109" s="1">
-        <v>20</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I109" s="1">
-        <v>0</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
-        <f t="shared" si="1"/>
-        <v>197</v>
-      </c>
-      <c r="B110" s="1">
-        <v>197</v>
-      </c>
-      <c r="C110" s="1">
-        <v>4</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G110" s="1">
-        <v>2</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I110" s="1">
-        <v>0</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>563</v>
-      </c>
-    </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
@@ -7310,39 +6562,6 @@
         <v>667</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
-        <f t="shared" si="2"/>
-        <v>182</v>
-      </c>
-      <c r="B122" s="1">
-        <v>182</v>
-      </c>
-      <c r="C122" s="1">
-        <v>18</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="G122" s="1">
-        <v>1</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I122" s="1">
-        <v>0</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>730</v>
-      </c>
-    </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <f t="shared" si="2"/>
@@ -7442,39 +6661,6 @@
         <v>664</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="B126" s="1">
-        <v>120</v>
-      </c>
-      <c r="C126" s="1">
-        <v>1</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G126" s="1">
-        <v>1</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I126" s="1">
-        <v>0</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <f t="shared" si="2"/>
@@ -8630,138 +7816,6 @@
         <v>738</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A162" s="1">
-        <f t="shared" si="2"/>
-        <v>352</v>
-      </c>
-      <c r="B162" s="1">
-        <v>352</v>
-      </c>
-      <c r="C162" s="1">
-        <v>19</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="G162" s="1">
-        <v>9</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I162" s="1">
-        <v>0</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
-        <f t="shared" si="2"/>
-        <v>353</v>
-      </c>
-      <c r="B163" s="1">
-        <v>353</v>
-      </c>
-      <c r="C163" s="1">
-        <v>19</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="G163" s="1">
-        <v>10</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I163" s="1">
-        <v>0</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <f t="shared" si="2"/>
-        <v>220</v>
-      </c>
-      <c r="B164" s="1">
-        <v>220</v>
-      </c>
-      <c r="C164" s="1">
-        <v>19</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G164" s="1">
-        <v>8</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I164" s="1">
-        <v>0</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A165" s="1">
-        <f t="shared" si="2"/>
-        <v>222</v>
-      </c>
-      <c r="B165" s="1">
-        <v>222</v>
-      </c>
-      <c r="C165" s="1">
-        <v>19</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="G165" s="1">
-        <v>6</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I165" s="1">
-        <v>0</v>
-      </c>
-      <c r="K165" s="1" t="s">
-        <v>735</v>
-      </c>
-    </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
@@ -10304,39 +9358,6 @@
         <v>534</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A212" s="1">
-        <f t="shared" si="3"/>
-        <v>81</v>
-      </c>
-      <c r="B212" s="1">
-        <v>81</v>
-      </c>
-      <c r="C212" s="1">
-        <v>4</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G212" s="1">
-        <v>15</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I212" s="1">
-        <v>1</v>
-      </c>
-      <c r="K212" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
@@ -10469,39 +9490,6 @@
         <v>618</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A217" s="1">
-        <f t="shared" si="3"/>
-        <v>82</v>
-      </c>
-      <c r="B217" s="1">
-        <v>82</v>
-      </c>
-      <c r="C217" s="1">
-        <v>4</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G217" s="1">
-        <v>23</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I217" s="1">
-        <v>1</v>
-      </c>
-      <c r="K217" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
@@ -12117,39 +11105,6 @@
       </c>
       <c r="K266" s="1" t="s">
         <v>658</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A267" s="1">
-        <f t="shared" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="B267" s="1">
-        <v>27</v>
-      </c>
-      <c r="C267" s="1">
-        <v>6</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="F267" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G267" s="1">
-        <v>1</v>
-      </c>
-      <c r="H267" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="I267" s="1">
-        <v>0</v>
-      </c>
-      <c r="K267" s="1" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
@@ -13952,7 +12907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C303"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$299</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="904">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2732,6 +2731,15 @@
   </si>
   <si>
     <t>Manage Version History</t>
+  </si>
+  <si>
+    <t>IID Dashboard</t>
+  </si>
+  <si>
+    <t>IID_Dashboard</t>
+  </si>
+  <si>
+    <t>IID/IID_Dashboard</t>
   </si>
 </sst>
 </file>
@@ -3068,7 +3076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K323"/>
+  <dimension ref="A1:K324"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -12033,7 +12041,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A323" si="4">B315</f>
+        <f t="shared" ref="A315:A324" si="4">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -12329,6 +12337,39 @@
       </c>
       <c r="K323" s="1" t="s">
         <v>898</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A324" s="4">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="B324" s="1">
+        <v>420</v>
+      </c>
+      <c r="C324" s="1">
+        <v>7</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="G324" s="1">
+        <v>1</v>
+      </c>
+      <c r="H324" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="I324" s="4">
+        <v>0</v>
+      </c>
+      <c r="K324" s="1" t="s">
+        <v>902</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="919">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2740,6 +2740,51 @@
   </si>
   <si>
     <t>IID/IID_Dashboard</t>
+  </si>
+  <si>
+    <t>loans exception</t>
+  </si>
+  <si>
+    <t>IID/loans_exception</t>
+  </si>
+  <si>
+    <t>loan transactions</t>
+  </si>
+  <si>
+    <t>IID/loan_transactions</t>
+  </si>
+  <si>
+    <t>loan documents</t>
+  </si>
+  <si>
+    <t>IID/loan_documents</t>
+  </si>
+  <si>
+    <t>Account exception</t>
+  </si>
+  <si>
+    <t>IID/Account_exception</t>
+  </si>
+  <si>
+    <t>Exceptions Reports</t>
+  </si>
+  <si>
+    <t>IID/Exceptions_Reports</t>
+  </si>
+  <si>
+    <t>Exceptions_Reports</t>
+  </si>
+  <si>
+    <t>account transaction</t>
+  </si>
+  <si>
+    <t>IID/account_transaction</t>
+  </si>
+  <si>
+    <t>account document</t>
+  </si>
+  <si>
+    <t>IID/account_document</t>
   </si>
 </sst>
 </file>
@@ -3076,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K324"/>
+  <dimension ref="A1:K331"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -12041,7 +12086,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A324" si="4">B315</f>
+        <f t="shared" ref="A315:A331" si="4">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -12370,6 +12415,237 @@
       </c>
       <c r="K324" s="1" t="s">
         <v>902</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A325" s="4">
+        <f t="shared" si="4"/>
+        <v>427</v>
+      </c>
+      <c r="B325" s="1">
+        <v>427</v>
+      </c>
+      <c r="C325" s="1">
+        <v>7</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="G325" s="1">
+        <v>11</v>
+      </c>
+      <c r="H325" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I325" s="1">
+        <v>0</v>
+      </c>
+      <c r="K325" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A326" s="4">
+        <f t="shared" si="4"/>
+        <v>426</v>
+      </c>
+      <c r="B326" s="1">
+        <v>426</v>
+      </c>
+      <c r="C326" s="1">
+        <v>7</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F326" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="G326" s="1">
+        <v>10</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I326" s="1">
+        <v>0</v>
+      </c>
+      <c r="K326" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A327" s="4">
+        <f t="shared" si="4"/>
+        <v>425</v>
+      </c>
+      <c r="B327" s="1">
+        <v>425</v>
+      </c>
+      <c r="C327" s="1">
+        <v>7</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G327" s="1">
+        <v>10</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I327" s="1">
+        <v>0</v>
+      </c>
+      <c r="K327" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A328" s="4">
+        <f t="shared" si="4"/>
+        <v>424</v>
+      </c>
+      <c r="B328" s="1">
+        <v>424</v>
+      </c>
+      <c r="C328" s="1">
+        <v>7</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="G328" s="1">
+        <v>8</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I328" s="1">
+        <v>0</v>
+      </c>
+      <c r="K328" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A329" s="4">
+        <f t="shared" si="4"/>
+        <v>423</v>
+      </c>
+      <c r="B329" s="1">
+        <v>423</v>
+      </c>
+      <c r="C329" s="1">
+        <v>7</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="G329" s="1">
+        <v>8</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I329" s="1">
+        <v>0</v>
+      </c>
+      <c r="K329" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A330" s="4">
+        <f t="shared" si="4"/>
+        <v>422</v>
+      </c>
+      <c r="B330" s="1">
+        <v>422</v>
+      </c>
+      <c r="C330" s="1">
+        <v>7</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="E330" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="G330" s="1">
+        <v>8</v>
+      </c>
+      <c r="H330" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I330" s="1">
+        <v>0</v>
+      </c>
+      <c r="K330" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A331" s="4">
+        <f t="shared" si="4"/>
+        <v>421</v>
+      </c>
+      <c r="B331" s="1">
+        <v>421</v>
+      </c>
+      <c r="C331" s="1">
+        <v>7</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="G331" s="1">
+        <v>7</v>
+      </c>
+      <c r="H331" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I331" s="1">
+        <v>0</v>
+      </c>
+      <c r="K331" s="1" t="s">
+        <v>672</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAS\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2057" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="928">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2785,6 +2785,33 @@
   </si>
   <si>
     <t>IID/account_document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OM </t>
+  </si>
+  <si>
+    <t>CAU/OM</t>
+  </si>
+  <si>
+    <t>PDP</t>
+  </si>
+  <si>
+    <t>CAU/PDF</t>
+  </si>
+  <si>
+    <t>ARPSE</t>
+  </si>
+  <si>
+    <t>CAU/Arpse</t>
+  </si>
+  <si>
+    <t>CAU WorkFlow</t>
+  </si>
+  <si>
+    <t>CAU/Workflow</t>
+  </si>
+  <si>
+    <t>WorkFlow</t>
   </si>
 </sst>
 </file>
@@ -3121,7 +3148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K331"/>
+  <dimension ref="A1:K335"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -12086,7 +12113,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A331" si="4">B315</f>
+        <f t="shared" ref="A315:A335" si="4">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -12648,7 +12675,140 @@
         <v>672</v>
       </c>
     </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A332" s="4">
+        <f t="shared" si="4"/>
+        <v>427</v>
+      </c>
+      <c r="B332" s="1">
+        <v>427</v>
+      </c>
+      <c r="C332" s="1">
+        <v>11</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="G332" s="1">
+        <v>1</v>
+      </c>
+      <c r="H332" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I332" s="1">
+        <v>0</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A333" s="4">
+        <f t="shared" si="4"/>
+        <v>428</v>
+      </c>
+      <c r="B333" s="1">
+        <v>428</v>
+      </c>
+      <c r="C333" s="1">
+        <v>11</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="G333" s="1">
+        <v>2</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I333" s="1">
+        <v>0</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A334" s="4">
+        <f t="shared" si="4"/>
+        <v>429</v>
+      </c>
+      <c r="B334" s="1">
+        <v>429</v>
+      </c>
+      <c r="C334" s="1">
+        <v>11</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="G334" s="1">
+        <v>3</v>
+      </c>
+      <c r="H334" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I334" s="1">
+        <v>0</v>
+      </c>
+      <c r="K334" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A335" s="4">
+        <f t="shared" si="4"/>
+        <v>430</v>
+      </c>
+      <c r="B335" s="1">
+        <v>430</v>
+      </c>
+      <c r="C335" s="1">
+        <v>11</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="G335" s="1">
+        <v>4</v>
+      </c>
+      <c r="H335" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I335" s="1">
+        <v>0</v>
+      </c>
+      <c r="K335" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:K3"/>
   <sortState ref="A2:L305">
     <sortCondition ref="F2:F305"/>
   </sortState>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="931">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -2812,6 +2812,15 @@
   </si>
   <si>
     <t>WorkFlow</t>
+  </si>
+  <si>
+    <t>Exception Report Addition</t>
+  </si>
+  <si>
+    <t>IID/Add_Exception_Reports</t>
+  </si>
+  <si>
+    <t>Add_Exception_Reports</t>
   </si>
 </sst>
 </file>
@@ -3148,7 +3157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K335"/>
+  <dimension ref="A1:K337"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
@@ -12113,7 +12122,7 @@
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A335" si="4">B315</f>
+        <f t="shared" ref="A315:A337" si="4">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -12805,6 +12814,72 @@
       </c>
       <c r="K335" s="1" t="s">
         <v>927</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A336" s="4">
+        <f t="shared" si="4"/>
+        <v>432</v>
+      </c>
+      <c r="B336" s="1">
+        <v>432</v>
+      </c>
+      <c r="C336" s="1">
+        <v>7</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="G336" s="1">
+        <v>1</v>
+      </c>
+      <c r="H336" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I336" s="1">
+        <v>0</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A337" s="4">
+        <f t="shared" si="4"/>
+        <v>431</v>
+      </c>
+      <c r="B337" s="1">
+        <v>431</v>
+      </c>
+      <c r="C337" s="1">
+        <v>7</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E337" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="G337" s="1">
+        <v>11</v>
+      </c>
+      <c r="H337" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I337" s="1">
+        <v>0</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/AIS/wwwroot/Images/Page ID.xlsx
+++ b/AIS/wwwroot/Images/Page ID.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IAS\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asad Ali\Documents\GitHub\HTTPS-IAS-Production\AIS\wwwroot\Images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9070"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="931">
   <si>
     <t>PAGE_NAME</t>
   </si>
@@ -3157,24 +3157,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K337"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K336"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="3.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="8.81640625" style="1"/>
+    <col min="2" max="2" width="3.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>792</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <f t="shared" ref="A2:A64" si="0">B2</f>
         <v>321</v>
@@ -3242,7 +3242,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <f t="shared" si="0"/>
         <v>265</v>
@@ -3275,7 +3275,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>207</v>
@@ -3308,7 +3308,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>324</v>
@@ -3341,7 +3341,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>258</v>
@@ -3374,7 +3374,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>217</v>
@@ -3407,7 +3407,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>218</v>
@@ -3440,7 +3440,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3473,7 +3473,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3506,7 +3506,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3539,7 +3539,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>251</v>
@@ -3572,7 +3572,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>278</v>
@@ -3605,7 +3605,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3638,7 +3638,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3671,7 +3671,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>206</v>
@@ -3704,7 +3704,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3737,7 +3737,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3770,7 +3770,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>225</v>
@@ -3803,7 +3803,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>215</v>
@@ -3836,7 +3836,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>191</v>
@@ -3869,7 +3869,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>262</v>
@@ -3902,7 +3902,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>323</v>
@@ -3935,7 +3935,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3968,7 +3968,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -4001,7 +4001,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -4034,7 +4034,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>96</v>
@@ -4067,7 +4067,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>240</v>
@@ -4100,7 +4100,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>90</v>
@@ -4133,7 +4133,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>91</v>
@@ -4166,7 +4166,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>241</v>
@@ -4199,7 +4199,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>202</v>
@@ -4232,7 +4232,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>254</v>
@@ -4265,7 +4265,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>198</v>
@@ -4298,7 +4298,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>242</v>
@@ -4331,7 +4331,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>248</v>
@@ -4364,7 +4364,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>293</v>
@@ -4397,7 +4397,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>199</v>
@@ -4430,7 +4430,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -4463,7 +4463,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>354</v>
@@ -4496,7 +4496,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>355</v>
@@ -4529,7 +4529,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -4562,7 +4562,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>74</v>
@@ -4595,7 +4595,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>73</v>
@@ -4628,7 +4628,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>71</v>
@@ -4661,7 +4661,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -4694,7 +4694,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -4727,7 +4727,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>72</v>
@@ -4760,7 +4760,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4793,7 +4793,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -4826,7 +4826,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -4859,7 +4859,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -4892,7 +4892,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>17</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>162</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>163</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>292</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>142</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>77</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>231</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>84</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>150</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>263</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>157</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>264</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>290</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>291</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>86</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>156</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>161</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>79</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>121</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>181</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>294</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>227</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>76</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>367</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>375</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A113" s="1">
         <v>374</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A114" s="1">
         <v>356</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A115" s="1">
         <v>325</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A116" s="1">
         <v>318</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A117" s="1">
         <v>320</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A118" s="1">
         <v>372</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A176" si="1">B119</f>
         <v>368</v>
@@ -5984,7 +5984,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>369</v>
@@ -6017,7 +6017,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>370</v>
@@ -6050,7 +6050,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>322</v>
@@ -6083,7 +6083,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>371</v>
@@ -6116,7 +6116,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>373</v>
@@ -6149,7 +6149,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>378</v>
@@ -6182,7 +6182,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>165</v>
@@ -6215,7 +6215,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>166</v>
@@ -6248,7 +6248,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>376</v>
@@ -6281,7 +6281,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>377</v>
@@ -6314,7 +6314,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>343</v>
@@ -6347,7 +6347,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A133" s="1">
         <f t="shared" si="1"/>
         <v>342</v>
@@ -6380,7 +6380,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A134" s="1">
         <f t="shared" si="1"/>
         <v>344</v>
@@ -6413,7 +6413,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A135" s="1">
         <f t="shared" si="1"/>
         <v>345</v>
@@ -6446,7 +6446,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A136" s="1">
         <f t="shared" si="1"/>
         <v>346</v>
@@ -6479,7 +6479,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A137" s="1">
         <f t="shared" si="1"/>
         <v>347</v>
@@ -6512,7 +6512,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A138" s="1">
         <f t="shared" si="1"/>
         <v>348</v>
@@ -6545,7 +6545,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A139" s="1">
         <f t="shared" si="1"/>
         <v>349</v>
@@ -6578,7 +6578,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A140" s="1">
         <f t="shared" si="1"/>
         <v>350</v>
@@ -6611,7 +6611,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A141" s="1">
         <f t="shared" si="1"/>
         <v>351</v>
@@ -6644,7 +6644,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A142" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -6677,7 +6677,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A143" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6710,7 +6710,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A144" s="1">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -6743,7 +6743,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A145" s="1">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -6776,7 +6776,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A146" s="1">
         <f t="shared" si="1"/>
         <v>67</v>
@@ -6809,7 +6809,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A147" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -6842,7 +6842,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A148" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -6875,7 +6875,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A149" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -6908,7 +6908,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A150" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6941,7 +6941,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A151" s="1">
         <f t="shared" si="1"/>
         <v>287</v>
@@ -6974,7 +6974,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A152" s="1">
         <f t="shared" si="1"/>
         <v>288</v>
@@ -7007,7 +7007,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A153" s="1">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -7040,7 +7040,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A154" s="1">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -7073,7 +7073,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A155" s="1">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -7106,7 +7106,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A156" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -7139,7 +7139,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A157" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -7172,7 +7172,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A158" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -7205,7 +7205,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A159" s="1">
         <f t="shared" si="1"/>
         <v>286</v>
@@ -7238,7 +7238,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A160" s="1">
         <f t="shared" si="1"/>
         <v>285</v>
@@ -7271,7 +7271,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A161" s="1">
         <f t="shared" si="1"/>
         <v>284</v>
@@ -7304,7 +7304,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A166" s="1">
         <f t="shared" si="1"/>
         <v>221</v>
@@ -7337,7 +7337,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A167" s="1">
         <f t="shared" si="1"/>
         <v>249</v>
@@ -7370,7 +7370,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A168" s="1">
         <f t="shared" si="1"/>
         <v>255</v>
@@ -7403,7 +7403,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A169" s="1">
         <f t="shared" si="1"/>
         <v>281</v>
@@ -7436,7 +7436,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A170" s="1">
         <f t="shared" si="1"/>
         <v>282</v>
@@ -7469,7 +7469,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A171" s="1">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -7502,7 +7502,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A172" s="1">
         <f t="shared" si="1"/>
         <v>176</v>
@@ -7535,7 +7535,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A173" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -7568,7 +7568,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A174" s="1">
         <f t="shared" si="1"/>
         <v>252</v>
@@ -7601,7 +7601,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A175" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -7634,7 +7634,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A176" s="1">
         <f t="shared" si="1"/>
         <v>268</v>
@@ -7667,7 +7667,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A177" s="1">
         <f t="shared" ref="A177:A240" si="2">B177</f>
         <v>168</v>
@@ -7700,7 +7700,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -7733,7 +7733,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -7766,7 +7766,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>117</v>
@@ -7799,7 +7799,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -7832,7 +7832,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>114</v>
@@ -7865,7 +7865,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -7898,7 +7898,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>230</v>
@@ -7931,7 +7931,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
         <v>276</v>
@@ -7964,7 +7964,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -7997,7 +7997,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -8030,7 +8030,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A188" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -8063,7 +8063,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
         <v>261</v>
@@ -8096,7 +8096,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>112</v>
@@ -8129,7 +8129,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A191" s="1">
         <f t="shared" si="2"/>
         <v>113</v>
@@ -8162,7 +8162,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A192" s="1">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -8195,7 +8195,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
         <f t="shared" si="2"/>
         <v>283</v>
@@ -8228,7 +8228,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
         <f t="shared" si="2"/>
         <v>116</v>
@@ -8261,7 +8261,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -8297,7 +8297,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A196" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -8330,7 +8330,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -8363,7 +8363,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A198" s="1">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -8396,7 +8396,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -8429,7 +8429,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A200" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -8462,7 +8462,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A201" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -8495,7 +8495,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A202" s="1">
         <f t="shared" si="2"/>
         <v>196</v>
@@ -8531,7 +8531,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A203" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -8564,7 +8564,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A204" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -8600,7 +8600,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A205" s="1">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -8636,7 +8636,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A206" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -8672,7 +8672,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A207" s="1">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -8708,7 +8708,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A208" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -8741,7 +8741,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A209" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -8777,7 +8777,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A210" s="1">
         <f t="shared" si="2"/>
         <v>267</v>
@@ -8813,7 +8813,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A211" s="1">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -8846,7 +8846,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A213" s="1">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -8879,7 +8879,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A214" s="1">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -8912,7 +8912,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A215" s="1">
         <f t="shared" si="2"/>
         <v>259</v>
@@ -8945,7 +8945,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A216" s="1">
         <f t="shared" si="2"/>
         <v>224</v>
@@ -8978,7 +8978,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A218" s="1">
         <f t="shared" si="2"/>
         <v>115</v>
@@ -9011,7 +9011,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A219" s="1">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -9044,7 +9044,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A220" s="1">
         <f t="shared" si="2"/>
         <v>232</v>
@@ -9077,7 +9077,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A221" s="1">
         <f t="shared" si="2"/>
         <v>110</v>
@@ -9110,7 +9110,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A222" s="1">
         <f t="shared" si="2"/>
         <v>306</v>
@@ -9143,7 +9143,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A223" s="1">
         <f t="shared" si="2"/>
         <v>109</v>
@@ -9176,7 +9176,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A224" s="1">
         <f t="shared" si="2"/>
         <v>205</v>
@@ -9209,7 +9209,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A225" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -9242,7 +9242,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A226" s="1">
         <f t="shared" si="2"/>
         <v>229</v>
@@ -9275,7 +9275,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A227" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -9308,7 +9308,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A228" s="1">
         <f t="shared" si="2"/>
         <v>302</v>
@@ -9341,7 +9341,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A229" s="1">
         <f t="shared" si="2"/>
         <v>279</v>
@@ -9374,7 +9374,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A230" s="1">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -9407,7 +9407,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A231" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -9440,7 +9440,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A232" s="1">
         <f t="shared" si="2"/>
         <v>250</v>
@@ -9473,7 +9473,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A233" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -9506,7 +9506,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A234" s="1">
         <f t="shared" si="2"/>
         <v>228</v>
@@ -9539,7 +9539,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A235" s="1">
         <f t="shared" si="2"/>
         <v>118</v>
@@ -9572,7 +9572,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A236" s="1">
         <f t="shared" si="2"/>
         <v>301</v>
@@ -9605,7 +9605,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A237" s="1">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -9638,7 +9638,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A238" s="1">
         <f t="shared" si="2"/>
         <v>119</v>
@@ -9671,7 +9671,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A239" s="1">
         <f t="shared" si="2"/>
         <v>108</v>
@@ -9704,7 +9704,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A240" s="1">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -9737,7 +9737,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A241" s="1">
         <f t="shared" ref="A241:A287" si="3">B241</f>
         <v>62</v>
@@ -9770,7 +9770,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -9803,7 +9803,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -9836,7 +9836,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>68</v>
@@ -9869,7 +9869,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>64</v>
@@ -9902,7 +9902,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>271</v>
@@ -9935,7 +9935,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>296</v>
@@ -9968,7 +9968,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>315</v>
@@ -10001,7 +10001,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>299</v>
@@ -10034,7 +10034,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>298</v>
@@ -10067,7 +10067,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>316</v>
@@ -10100,7 +10100,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>297</v>
@@ -10133,7 +10133,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>381</v>
@@ -10166,7 +10166,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>317</v>
@@ -10199,7 +10199,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>295</v>
@@ -10232,7 +10232,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>304</v>
@@ -10265,7 +10265,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>303</v>
@@ -10298,7 +10298,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>300</v>
@@ -10331,7 +10331,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A259" s="1">
         <f t="shared" si="3"/>
         <v>319</v>
@@ -10364,7 +10364,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A260" s="1">
         <f t="shared" si="3"/>
         <v>380</v>
@@ -10397,7 +10397,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A261" s="1">
         <f t="shared" si="3"/>
         <v>305</v>
@@ -10430,7 +10430,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A262" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -10463,7 +10463,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A263" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -10496,7 +10496,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A264" s="1">
         <f t="shared" si="3"/>
         <v>273</v>
@@ -10529,7 +10529,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A265" s="1">
         <f t="shared" si="3"/>
         <v>275</v>
@@ -10562,7 +10562,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A266" s="1">
         <f t="shared" si="3"/>
         <v>277</v>
@@ -10595,7 +10595,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A268" s="1">
         <f t="shared" si="3"/>
         <v>269</v>
@@ -10628,7 +10628,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A269" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -10661,7 +10661,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A270" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -10694,7 +10694,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A271" s="1">
         <f t="shared" si="3"/>
         <v>270</v>
@@ -10727,7 +10727,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A272" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -10760,7 +10760,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A273" s="1">
         <f t="shared" si="3"/>
         <v>31</v>
@@ -10793,7 +10793,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A274" s="1">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -10826,7 +10826,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A275" s="1">
         <f t="shared" si="3"/>
         <v>28</v>
@@ -10859,7 +10859,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A276" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -10892,7 +10892,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A277" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -10925,7 +10925,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A278" s="1">
         <f t="shared" si="3"/>
         <v>272</v>
@@ -10958,7 +10958,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A279" s="1">
         <f t="shared" si="3"/>
         <v>274</v>
@@ -10991,7 +10991,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A280" s="1">
         <f t="shared" si="3"/>
         <v>29</v>
@@ -11024,7 +11024,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A281" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -11057,7 +11057,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A282" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -11090,7 +11090,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A283" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -11123,7 +11123,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A284" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -11156,7 +11156,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A285" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -11189,7 +11189,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A286" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -11222,7 +11222,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A287" s="1">
         <f t="shared" si="3"/>
         <v>266</v>
@@ -11252,7 +11252,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A288" s="1">
         <v>382</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A289" s="1">
         <v>383</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A290" s="1">
         <v>384</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A291" s="1">
         <v>385</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A292" s="1">
         <v>0</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A293" s="1">
         <v>392</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A294" s="1">
         <v>386</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A295" s="1">
         <v>387</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A296" s="1">
         <v>388</v>
       </c>
@@ -11540,7 +11540,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A297" s="1">
         <v>389</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A298" s="1">
         <v>390</v>
       </c>
@@ -11604,7 +11604,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A299" s="1">
         <v>391</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A300" s="1">
         <v>394</v>
       </c>
@@ -11668,7 +11668,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A301" s="1">
         <v>395</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A302" s="1">
         <v>396</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A303" s="1">
         <v>393</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A304" s="1">
         <v>400</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A305" s="1">
         <v>401</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A306" s="1">
         <v>402</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A307" s="1">
         <v>403</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A308" s="1">
         <v>404</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A309" s="1">
         <v>405</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A310" s="1">
         <v>406</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A311" s="1">
         <f>B311</f>
         <v>407</v>
@@ -12021,7 +12021,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A312" s="1">
         <f>B312</f>
         <v>408</v>
@@ -12054,7 +12054,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A313" s="1">
         <f>B313</f>
         <v>398</v>
@@ -12087,7 +12087,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A314" s="1">
         <f>B314</f>
         <v>409</v>
@@ -12120,9 +12120,9 @@
         <v>866</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" ht="15" x14ac:dyDescent="0.4">
       <c r="A315" s="4">
-        <f t="shared" ref="A315:A337" si="4">B315</f>
+        <f t="shared" ref="A315:A336" si="4">B315</f>
         <v>410</v>
       </c>
       <c r="B315" s="4">
@@ -12154,7 +12154,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A316" s="4">
         <f t="shared" si="4"/>
         <v>411</v>
@@ -12188,7 +12188,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A317" s="4">
         <f t="shared" si="4"/>
         <v>412</v>
@@ -12222,7 +12222,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A318" s="4">
         <f t="shared" si="4"/>
         <v>398</v>
@@ -12255,7 +12255,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A319" s="1">
         <f t="shared" si="4"/>
         <v>413</v>
@@ -12288,7 +12288,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A320" s="4">
         <f t="shared" si="4"/>
         <v>414</v>
@@ -12321,7 +12321,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A321" s="4">
         <f t="shared" si="4"/>
         <v>415</v>
@@ -12354,7 +12354,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A322" s="4">
         <f t="shared" si="4"/>
         <v>416</v>
@@ -12387,7 +12387,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A323" s="1">
         <f t="shared" si="4"/>
         <v>419</v>
@@ -12420,7 +12420,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A324" s="4">
         <f t="shared" si="4"/>
         <v>420</v>
@@ -12453,28 +12453,28 @@
         <v>902</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A325" s="4">
         <f t="shared" si="4"/>
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B325" s="1">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C325" s="1">
         <v>7</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="E325" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="G325" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H325" s="1" t="s">
         <v>690</v>
@@ -12483,28 +12483,28 @@
         <v>0</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A326" s="4">
         <f t="shared" si="4"/>
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B326" s="1">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C326" s="1">
         <v>7</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E326" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="G326" s="1">
         <v>10</v>
@@ -12516,31 +12516,31 @@
         <v>0</v>
       </c>
       <c r="K326" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A327" s="4">
         <f t="shared" si="4"/>
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B327" s="1">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C327" s="1">
         <v>7</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="E327" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G327" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H327" s="1" t="s">
         <v>690</v>
@@ -12549,28 +12549,28 @@
         <v>0</v>
       </c>
       <c r="K327" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A328" s="4">
         <f t="shared" si="4"/>
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B328" s="1">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C328" s="1">
         <v>7</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E328" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G328" s="1">
         <v>8</v>
@@ -12582,28 +12582,28 @@
         <v>0</v>
       </c>
       <c r="K328" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A329" s="4">
         <f t="shared" si="4"/>
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B329" s="1">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C329" s="1">
         <v>7</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="G329" s="1">
         <v>8</v>
@@ -12615,31 +12615,31 @@
         <v>0</v>
       </c>
       <c r="K329" s="1" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A330" s="4">
         <f t="shared" si="4"/>
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B330" s="1">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C330" s="1">
         <v>7</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="E330" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G330" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H330" s="1" t="s">
         <v>690</v>
@@ -12648,31 +12648,31 @@
         <v>0</v>
       </c>
       <c r="K330" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A331" s="4">
         <f t="shared" si="4"/>
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B331" s="1">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C331" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="E331" s="4" t="s">
-        <v>806</v>
+        <v>919</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>797</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="G331" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H331" s="1" t="s">
         <v>690</v>
@@ -12681,31 +12681,31 @@
         <v>0</v>
       </c>
       <c r="K331" s="1" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A332" s="4">
         <f t="shared" si="4"/>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B332" s="1">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C332" s="1">
         <v>11</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>797</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="G332" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H332" s="1" t="s">
         <v>690</v>
@@ -12714,31 +12714,31 @@
         <v>0</v>
       </c>
       <c r="K332" s="1" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A333" s="4">
         <f t="shared" si="4"/>
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B333" s="1">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C333" s="1">
         <v>11</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>797</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G333" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H333" s="1" t="s">
         <v>690</v>
@@ -12747,31 +12747,31 @@
         <v>0</v>
       </c>
       <c r="K333" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A334" s="4">
         <f t="shared" si="4"/>
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B334" s="1">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C334" s="1">
         <v>11</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>797</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="G334" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H334" s="1" t="s">
         <v>690</v>
@@ -12780,31 +12780,31 @@
         <v>0</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A335" s="4">
         <f t="shared" si="4"/>
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B335" s="1">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C335" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="G335" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H335" s="1" t="s">
         <v>690</v>
@@ -12813,31 +12813,31 @@
         <v>0</v>
       </c>
       <c r="K335" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A336" s="4">
         <f t="shared" si="4"/>
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B336" s="1">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C336" s="1">
         <v>7</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="E336" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E336" s="4" t="s">
         <v>806</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
       <c r="G336" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H336" s="1" t="s">
         <v>690</v>
@@ -12846,39 +12846,6 @@
         <v>0</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A337" s="4">
-        <f t="shared" si="4"/>
-        <v>431</v>
-      </c>
-      <c r="B337" s="1">
-        <v>431</v>
-      </c>
-      <c r="C337" s="1">
-        <v>7</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="E337" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="G337" s="1">
-        <v>11</v>
-      </c>
-      <c r="H337" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="I337" s="1">
-        <v>0</v>
-      </c>
-      <c r="K337" s="1" t="s">
         <v>683</v>
       </c>
     </row>
@@ -12894,17 +12861,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C303"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="44.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>794</v>
       </c>
@@ -12912,7 +12879,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>794</v>
       </c>
@@ -12920,7 +12887,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>794</v>
       </c>
@@ -12928,7 +12895,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>794</v>
       </c>
@@ -12936,7 +12903,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>794</v>
       </c>
@@ -12944,7 +12911,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>794</v>
       </c>
@@ -12952,7 +12919,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>794</v>
       </c>
@@ -12960,7 +12927,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>794</v>
       </c>
@@ -12968,7 +12935,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>794</v>
       </c>
@@ -12976,7 +12943,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>794</v>
       </c>
@@ -12984,7 +12951,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>794</v>
       </c>
@@ -12992,7 +12959,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>794</v>
       </c>
@@ -13000,7 +12967,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>794</v>
       </c>
@@ -13008,7 +12975,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>794</v>
       </c>
@@ -13016,7 +12983,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>794</v>
       </c>
@@ -13024,7 +12991,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>794</v>
       </c>
@@ -13032,7 +12999,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>794</v>
       </c>
@@ -13040,7 +13007,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>794</v>
       </c>
@@ -13048,7 +13015,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>794</v>
       </c>
@@ -13056,7 +13023,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>794</v>
       </c>
@@ -13064,7 +13031,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>794</v>
       </c>
@@ -13072,7 +13039,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>794</v>
       </c>
@@ -13080,7 +13047,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>794</v>
       </c>
@@ -13088,7 +13055,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>794</v>
       </c>
@@ -13096,7 +13063,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>794</v>
       </c>
@@ -13104,7 +13071,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>794</v>
       </c>
@@ -13112,7 +13079,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>794</v>
       </c>
@@ -13120,7 +13087,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>795</v>
       </c>
@@ -13128,7 +13095,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>795</v>
       </c>
@@ -13136,7 +13103,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>795</v>
       </c>
@@ -13144,7 +13111,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>795</v>
       </c>
@@ -13152,7 +13119,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>796</v>
       </c>
@@ -13160,7 +13127,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>796</v>
       </c>
@@ -13168,7 +13135,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>797</v>
       </c>
@@ -13179,7 +13146,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>797</v>
       </c>
@@ -13190,7 +13157,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>11</v>
       </c>
@@ -13198,7 +13165,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
         <v>426</v>
       </c>
@@ -13206,7 +13173,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>11</v>
       </c>
@@ -13214,7 +13181,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>426</v>
       </c>
@@ -13222,7 +13189,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
@@ -13230,7 +13197,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>11</v>
       </c>
@@ -13238,7 +13205,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
         <v>11</v>
       </c>
@@ -13246,7 +13213,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>11</v>
       </c>
@@ -13254,7 +13221,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>426</v>
       </c>
@@ -13262,7 +13229,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>426</v>
       </c>
@@ -13270,7 +13237,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
         <v>11</v>
       </c>
@@ -13278,7 +13245,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>11</v>
       </c>
@@ -13286,7 +13253,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>11</v>
       </c>
@@ -13294,7 +13261,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>426</v>
       </c>
@@ -13302,7 +13269,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
@@ -13310,7 +13277,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>800</v>
       </c>
@@ -13318,7 +13285,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>800</v>
       </c>
@@ -13326,7 +13293,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>801</v>
       </c>
@@ -13334,7 +13301,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>801</v>
       </c>
@@ -13342,7 +13309,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>801</v>
       </c>
@@ -13350,7 +13317,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>801</v>
       </c>
@@ -13358,7 +13325,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>801</v>
       </c>
@@ -13366,7 +13333,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>801</v>
       </c>
@@ -13374,7 +13341,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>801</v>
       </c>
@@ -13382,7 +13349,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>801</v>
       </c>
@@ -13390,7 +13357,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>801</v>
       </c>
@@ -13398,7 +13365,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>801</v>
       </c>
@@ -13406,7 +13373,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>802</v>
       </c>
@@ -13414,7 +13381,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>802</v>
       </c>
@@ -13422,7 +13389,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>802</v>
       </c>
@@ -13430,7 +13397,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>802</v>
       </c>
@@ -13438,7 +13405,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>802</v>
       </c>
@@ -13446,7 +13413,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>802</v>
       </c>
@@ -13454,7 +13421,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
         <v>802</v>
       </c>
@@ -13462,7 +13429,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
         <v>802</v>
       </c>
@@ -13470,7 +13437,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>802</v>
       </c>
@@ -13478,7 +13445,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
         <v>802</v>
       </c>
@@ -13486,7 +13453,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>802</v>
       </c>
@@ -13494,7 +13461,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>802</v>
       </c>
@@ -13502,7 +13469,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>802</v>
       </c>
@@ -13510,7 +13477,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
         <v>802</v>
       </c>
@@ -13518,7 +13485,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>802</v>
       </c>
@@ -13526,7 +13493,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
         <v>802</v>
       </c>
@@ -13534,7 +13501,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>802</v>
       </c>
@@ -13542,7 +13509,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
         <v>802</v>
       </c>
@@ -13550,7 +13517,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>802</v>
       </c>
@@ -13558,7 +13525,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
         <v>802</v>
       </c>
@@ -13566,7 +13533,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>802</v>
       </c>
@@ -13574,7 +13541,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
         <v>802</v>
       </c>
@@ -13582,7 +13549,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
         <v>802</v>
       </c>
@@ -13590,7 +13557,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>802</v>
       </c>
@@ -13598,7 +13565,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
         <v>802</v>
       </c>
@@ -13606,7 +13573,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>802</v>
       </c>
@@ -13614,7 +13581,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>802</v>
       </c>
@@ -13622,7 +13589,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>802</v>
       </c>
@@ -13630,7 +13597,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
         <v>802</v>
       </c>
@@ -13638,7 +13605,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>802</v>
       </c>
@@ -13646,7 +13613,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
         <v>802</v>
       </c>
@@ -13654,7 +13621,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" s="1" t="s">
         <v>802</v>
       </c>
@@ -13662,7 +13629,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" s="1" t="s">
         <v>802</v>
       </c>
@@ -13670,7 +13637,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="1" t="s">
         <v>802</v>
       </c>
@@ -13678,7 +13645,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="1" t="s">
         <v>802</v>
       </c>
@@ -13686,7 +13653,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="1" t="s">
         <v>802</v>
       </c>
@@ -13694,7 +13661,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" s="1" t="s">
         <v>802</v>
       </c>
@@ -13702,7 +13669,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" s="1" t="s">
         <v>802</v>
       </c>
@@ -13710,7 +13677,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" s="1" t="s">
         <v>802</v>
       </c>
@@ -13718,7 +13685,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
         <v>802</v>
       </c>
@@ -13726,7 +13693,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
         <v>802</v>
       </c>
@@ -13734,7 +13701,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" s="1" t="s">
         <v>802</v>
       </c>
@@ -13742,7 +13709,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" s="1" t="s">
         <v>802</v>
       </c>
@@ -13750,7 +13717,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" s="1" t="s">
         <v>802</v>
       </c>
@@ -13758,7 +13725,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
         <v>802</v>
       </c>
@@ -13766,7 +13733,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" s="1" t="s">
         <v>802</v>
       </c>
@@ -13774,7 +13741,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
         <v>802</v>
       </c>
@@ -13782,7 +13749,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" s="1" t="s">
         <v>802</v>
       </c>
@@ -13790,7 +13757,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" s="1" t="s">
         <v>803</v>
       </c>
@@ -13798,7 +13765,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" s="1" t="s">
         <v>803</v>
       </c>
@@ -13806,7 +13773,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" s="1" t="s">
         <v>803</v>
       </c>
@@ -13814,7 +13781,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" s="1" t="s">
         <v>803</v>
       </c>
@@ -13822,7 +13789,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" s="1" t="s">
         <v>803</v>
       </c>
@@ -13830,7 +13797,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" s="1" t="s">
         <v>803</v>
       </c>
@@ -13838,7 +13805,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" s="1" t="s">
         <v>803</v>
       </c>
@@ -13846,7 +13813,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" s="1" t="s">
         <v>803</v>
       </c>
@@ -13854,7 +13821,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" s="1" t="s">
         <v>803</v>
       </c>
@@ -13862,7 +13829,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" s="1" t="s">
         <v>803</v>
       </c>
@@ -13870,7 +13837,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" s="1" t="s">
         <v>803</v>
       </c>
@@ -13878,7 +13845,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" s="1" t="s">
         <v>803</v>
       </c>
@@ -13886,7 +13853,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" s="1" t="s">
         <v>803</v>
       </c>
@@ -13894,7 +13861,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" s="1" t="s">
         <v>803</v>
       </c>
@@ -13902,7 +13869,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" s="1" t="s">
         <v>803</v>
       </c>
@@ -13910,7 +13877,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" s="1" t="s">
         <v>804</v>
       </c>
@@ -13918,7 +13885,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" s="1" t="s">
         <v>803</v>
       </c>
@@ -13926,7 +13893,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" s="1" t="s">
         <v>803</v>
       </c>
@@ -13934,7 +13901,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" s="1" t="s">
         <v>803</v>
       </c>
@@ -13942,7 +13909,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" s="1" t="s">
         <v>803</v>
       </c>
@@ -13950,7 +13917,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" s="1" t="s">
         <v>803</v>
       </c>
@@ -13958,7 +13925,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" s="1" t="s">
         <v>803</v>
       </c>
@@ -13966,7 +13933,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" s="1" t="s">
         <v>803</v>
       </c>
@@ -13974,7 +13941,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" s="1" t="s">
         <v>803</v>
       </c>
@@ -13982,7 +13949,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" s="1" t="s">
         <v>803</v>
       </c>
@@ -13990,7 +13957,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" s="1" t="s">
         <v>803</v>
       </c>
@@ -13998,7 +13965,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" s="1" t="s">
         <v>803</v>
       </c>
@@ -14006,7 +13973,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" s="1" t="s">
         <v>803</v>
       </c>
@@ -14014,7 +13981,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" s="1" t="s">
         <v>803</v>
       </c>
@@ -14022,7 +13989,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" s="1" t="s">
         <v>803</v>
       </c>
@@ -14030,7 +13997,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" s="1" t="s">
         <v>803</v>
       </c>
@@ -14038,7 +14005,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" s="1" t="s">
         <v>805</v>
       </c>
@@ -14046,7 +14013,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" s="1" t="s">
         <v>805</v>
       </c>
@@ -14054,7 +14021,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" s="1" t="s">
         <v>805</v>
       </c>
@@ -14062,7 +14029,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" s="1" t="s">
         <v>805</v>
       </c>
@@ -14070,7 +14037,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" s="1" t="s">
         <v>805</v>
       </c>
@@ -14078,7 +14045,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" s="1" t="s">
         <v>805</v>
       </c>
@@ -14086,7 +14053,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" s="1" t="s">
         <v>806</v>
       </c>
@@ -14094,7 +14061,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" s="1" t="s">
         <v>806</v>
       </c>
@@ -14102,7 +14069,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" s="1" t="s">
         <v>806</v>
       </c>
@@ -14110,7 +14077,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" s="1" t="s">
         <v>806</v>
       </c>
@@ -14118,7 +14085,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" s="1" t="s">
         <v>806</v>
       </c>
@@ -14126,7 +14093,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" s="1" t="s">
         <v>806</v>
       </c>
@@ -14134,7 +14101,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" s="1" t="s">
         <v>806</v>
       </c>
@@ -14142,7 +14109,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" s="1" t="s">
         <v>806</v>
       </c>
@@ -14150,7 +14117,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" s="1" t="s">
         <v>806</v>
       </c>
@@ -14158,7 +14125,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" s="1" t="s">
         <v>807</v>
       </c>
@@ -14166,7 +14133,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" s="1" t="s">
         <v>808</v>
       </c>
@@ -14174,7 +14141,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" s="1" t="s">
         <v>808</v>
       </c>
@@ -14182,7 +14149,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" s="1" t="s">
         <v>808</v>
       </c>
@@ -14190,7 +14157,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" s="1" t="s">
         <v>808</v>
       </c>
@@ -14198,7 +14165,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" s="1" t="s">
         <v>808</v>
       </c>
@@ -14206,7 +14173,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" s="1" t="s">
         <v>808</v>
       </c>
@@ -14214,7 +14181,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" s="1" t="s">
         <v>808</v>
       </c>
@@ -14222,7 +14189,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" s="1" t="s">
         <v>808</v>
       </c>
@@ -14230,7 +14197,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" s="1" t="s">
         <v>808</v>
       </c>
@@ -14238,7 +14205,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" s="1" t="s">
         <v>808</v>
       </c>
@@ -14246,7 +14213,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" s="1" t="s">
         <v>808</v>
       </c>
@@ -14254,7 +14221,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" s="1" t="s">
         <v>808</v>
       </c>
@@ -14262,7 +14229,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" s="1" t="s">
         <v>808</v>
       </c>
@@ -14270,7 +14237,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" s="1" t="s">
         <v>808</v>
       </c>
@@ -14278,7 +14245,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" s="1" t="s">
         <v>808</v>
       </c>
@@ -14286,7 +14253,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" s="1" t="s">
         <v>808</v>
       </c>
@@ -14294,7 +14261,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" s="1" t="s">
         <v>808</v>
       </c>
@@ -14302,7 +14269,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" s="1" t="s">
         <v>809</v>
       </c>
@@ -14310,7 +14277,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" s="1" t="s">
         <v>809</v>
       </c>
@@ -14318,7 +14285,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" s="1" t="s">
         <v>809</v>
       </c>
@@ -14326,7 +14293,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" s="1" t="s">
         <v>809</v>
       </c>
@@ -14334,7 +14301,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" s="1" t="s">
         <v>809</v>
       </c>
@@ -14342,7 +14309,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" s="1" t="s">
         <v>809</v>
       </c>
@@ -14350,7 +14317,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" s="1" t="s">
         <v>809</v>
       </c>
@@ -14358,7 +14325,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" s="1" t="s">
         <v>809</v>
       </c>
@@ -14366,7 +14333,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" s="1" t="s">
         <v>809</v>
       </c>
@@ -14374,7 +14341,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" s="1" t="s">
         <v>809</v>
       </c>
@@ -14382,7 +14349,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" s="1" t="s">
         <v>809</v>
       </c>
@@ -14390,7 +14357,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" s="1" t="s">
         <v>809</v>
       </c>
@@ -14398,7 +14365,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" s="1" t="s">
         <v>99</v>
       </c>
@@ -14406,7 +14373,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" s="1" t="s">
         <v>99</v>
       </c>
@@ -14414,7 +14381,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" s="1" t="s">
         <v>99</v>
       </c>
@@ -14422,7 +14389,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" s="1" t="s">
         <v>99</v>
       </c>
@@ -14430,7 +14397,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" s="1" t="s">
         <v>99</v>
       </c>
@@ -14438,7 +14405,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" s="1" t="s">
         <v>99</v>
       </c>
@@ -14446,7 +14413,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" s="1" t="s">
         <v>99</v>
       </c>
@@ -14454,7 +14421,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" s="1" t="s">
         <v>99</v>
       </c>
@@ -14462,7 +14429,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" s="1" t="s">
         <v>99</v>
       </c>
@@ -14470,7 +14437,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" s="1" t="s">
         <v>99</v>
       </c>
@@ -14478,7 +14445,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" s="1" t="s">
         <v>99</v>
       </c>
@@ -14486,7 +14453,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" s="1" t="s">
         <v>99</v>
       </c>
@@ -14494,7 +14461,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" s="1" t="s">
         <v>99</v>
       </c>
@@ -14502,7 +14469,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" s="1" t="s">
         <v>99</v>
       </c>
@@ -14510,7 +14477,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
         <v>99</v>
       </c>
@@ -14518,7 +14485,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" s="1" t="s">
         <v>99</v>
       </c>
@@ -14526,7 +14493,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" s="1" t="s">
         <v>99</v>
       </c>
@@ -14534,7 +14501,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" s="1" t="s">
         <v>99</v>
       </c>
@@ -14542,7 +14509,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" s="1" t="s">
         <v>99</v>
       </c>
@@ -14550,7 +14517,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" s="1" t="s">
         <v>99</v>
       </c>
@@ -14558,7 +14525,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" s="1" t="s">
         <v>99</v>
       </c>
@@ -14566,7 +14533,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" s="1" t="s">
         <v>99</v>
       </c>
@@ -14574,7 +14541,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" s="1" t="s">
         <v>99</v>
       </c>
@@ -14582,7 +14549,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" s="1" t="s">
         <v>99</v>
       </c>
@@ -14590,7 +14557,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" s="1" t="s">
         <v>99</v>
       </c>
@@ -14598,7 +14565,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" s="1" t="s">
         <v>99</v>
       </c>
@@ -14606,7 +14573,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" s="1" t="s">
         <v>99</v>
       </c>
@@ -14614,7 +14581,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" s="1" t="s">
         <v>99</v>
       </c>
@@ -14622,7 +14589,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" s="1" t="s">
         <v>99</v>
       </c>
@@ -14630,7 +14597,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" s="1" t="s">
         <v>99</v>
       </c>
@@ -14638,7 +14605,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" s="1" t="s">
         <v>99</v>
       </c>
@@ -14646,7 +14613,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" s="1" t="s">
         <v>99</v>
       </c>
@@ -14654,7 +14621,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" s="1" t="s">
         <v>99</v>
       </c>
@@ -14662,7 +14629,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" s="1" t="s">
         <v>99</v>
       </c>
@@ -14670,7 +14637,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" s="1" t="s">
         <v>99</v>
       </c>
@@ -14678,7 +14645,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" s="1" t="s">
         <v>99</v>
       </c>
@@ -14686,7 +14653,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" s="1" t="s">
         <v>99</v>
       </c>
@@ -14694,7 +14661,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" s="1" t="s">
         <v>99</v>
       </c>
@@ -14702,7 +14669,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" s="1" t="s">
         <v>99</v>
       </c>
@@ -14710,7 +14677,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" s="1" t="s">
         <v>99</v>
       </c>
@@ -14718,7 +14685,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" s="1" t="s">
         <v>99</v>
       </c>
@@ -14726,7 +14693,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" s="1" t="s">
         <v>99</v>
       </c>
@@ -14734,7 +14701,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" s="1" t="s">
         <v>99</v>
       </c>
@@ -14742,7 +14709,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" s="1" t="s">
         <v>99</v>
       </c>
@@ -14750,7 +14717,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" s="1" t="s">
         <v>99</v>
       </c>
@@ -14758,7 +14725,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" s="1" t="s">
         <v>99</v>
       </c>
@@ -14766,7 +14733,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" s="1" t="s">
         <v>99</v>
       </c>
@@ -14774,7 +14741,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" s="1" t="s">
         <v>99</v>
       </c>
@@ -14782,7 +14749,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" s="1" t="s">
         <v>99</v>
       </c>
@@ -14790,7 +14757,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" s="1" t="s">
         <v>99</v>
       </c>
@@ -14798,7 +14765,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" s="1" t="s">
         <v>99</v>
       </c>
@@ -14806,7 +14773,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" s="1" t="s">
         <v>99</v>
       </c>
@@ -14814,7 +14781,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" s="1" t="s">
         <v>99</v>
       </c>
@@ -14822,7 +14789,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" s="1" t="s">
         <v>99</v>
       </c>
@@ -14830,7 +14797,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" s="1" t="s">
         <v>99</v>
       </c>
@@ -14838,7 +14805,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" s="1" t="s">
         <v>99</v>
       </c>
@@ -14846,7 +14813,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" s="1" t="s">
         <v>99</v>
       </c>
@@ -14854,7 +14821,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" s="1" t="s">
         <v>99</v>
       </c>
@@ -14862,7 +14829,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" s="1" t="s">
         <v>99</v>
       </c>
@@ -14870,7 +14837,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" s="1" t="s">
         <v>99</v>
       </c>
@@ -14878,7 +14845,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" s="1" t="s">
         <v>99</v>
       </c>
@@ -14886,7 +14853,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" s="1" t="s">
         <v>99</v>
       </c>
@@ -14894,7 +14861,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" s="1" t="s">
         <v>99</v>
       </c>
@@ -14902,7 +14869,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" s="1" t="s">
         <v>99</v>
       </c>
@@ -14910,7 +14877,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" s="1" t="s">
         <v>99</v>
       </c>
@@ -14918,7 +14885,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" s="1" t="s">
         <v>99</v>
       </c>
@@ -14926,7 +14893,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" s="1" t="s">
         <v>99</v>
       </c>
@@ -14934,7 +14901,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" s="1" t="s">
         <v>99</v>
       </c>
@@ -14942,7 +14909,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" s="1" t="s">
         <v>99</v>
       </c>
@@ -14950,7 +14917,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" s="1" t="s">
         <v>810</v>
       </c>
@@ -14958,7 +14925,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" s="1" t="s">
         <v>810</v>
       </c>
@@ -14966,7 +14933,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" s="1" t="s">
         <v>810</v>
       </c>
@@ -14974,7 +14941,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" s="1" t="s">
         <v>810</v>
       </c>
@@ -14982,7 +14949,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" s="1" t="s">
         <v>810</v>
       </c>
@@ -14990,7 +14957,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" s="1" t="s">
         <v>810</v>
       </c>
@@ -14998,7 +14965,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" s="1" t="s">
         <v>810</v>
       </c>
@@ -15006,7 +14973,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" s="1" t="s">
         <v>811</v>
       </c>
@@ -15014,7 +14981,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" s="1" t="s">
         <v>811</v>
       </c>
@@ -15022,7 +14989,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" s="1" t="s">
         <v>811</v>
       </c>
@@ -15030,7 +14997,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" s="1" t="s">
         <v>811</v>
       </c>
@@ -15038,7 +15005,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" s="1" t="s">
         <v>811</v>
       </c>
@@ -15046,7 +15013,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" s="1" t="s">
         <v>811</v>
       </c>
@@ -15054,7 +15021,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" s="1" t="s">
         <v>811</v>
       </c>
@@ -15062,7 +15029,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" s="1" t="s">
         <v>811</v>
       </c>
@@ -15070,7 +15037,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" s="1" t="s">
         <v>811</v>
       </c>
@@ -15078,7 +15045,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" s="1" t="s">
         <v>811</v>
       </c>
@@ -15086,7 +15053,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" s="1" t="s">
         <v>811</v>
       </c>
@@ -15094,7 +15061,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" s="1" t="s">
         <v>811</v>
       </c>
@@ -15102,7 +15069,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" s="1" t="s">
         <v>811</v>
       </c>
@@ -15110,7 +15077,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" s="1" t="s">
         <v>811</v>
       </c>
@@ -15118,7 +15085,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" s="1" t="s">
         <v>811</v>
       </c>
@@ -15126,7 +15093,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" s="1" t="s">
         <v>812</v>
       </c>
@@ -15134,7 +15101,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" s="1" t="s">
         <v>812</v>
       </c>
@@ -15142,7 +15109,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" s="1" t="s">
         <v>812</v>
       </c>
@@ -15150,7 +15117,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" s="1" t="s">
         <v>812</v>
       </c>
@@ -15158,7 +15125,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" s="1" t="s">
         <v>812</v>
       </c>
@@ -15166,7 +15133,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" s="1" t="s">
         <v>812</v>
       </c>
@@ -15174,7 +15141,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" s="1" t="s">
         <v>812</v>
       </c>
@@ -15182,7 +15149,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" s="1" t="s">
         <v>812</v>
       </c>
@@ -15190,7 +15157,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" s="1" t="s">
         <v>812</v>
       </c>
@@ -15198,7 +15165,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" s="1" t="s">
         <v>812</v>
       </c>
@@ -15206,7 +15173,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" s="1" t="s">
         <v>812</v>
       </c>
@@ -15214,7 +15181,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" s="1" t="s">
         <v>812</v>
       </c>
@@ -15222,7 +15189,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" s="1" t="s">
         <v>812</v>
       </c>
@@ -15230,7 +15197,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" s="1" t="s">
         <v>812</v>
       </c>
@@ -15238,7 +15205,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" s="1" t="s">
         <v>812</v>
       </c>
@@ -15246,7 +15213,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" s="1" t="s">
         <v>812</v>
       </c>
@@ -15254,7 +15221,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" s="1" t="s">
         <v>812</v>
       </c>
@@ -15262,7 +15229,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" s="1" t="s">
         <v>812</v>
       </c>
@@ -15270,7 +15237,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" s="1" t="s">
         <v>812</v>
       </c>
@@ -15278,7 +15245,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" s="1" t="s">
         <v>812</v>
       </c>
@@ -15286,7 +15253,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" s="1" t="s">
         <v>813</v>
       </c>
@@ -15294,7 +15261,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" s="1" t="s">
         <v>813</v>
       </c>
@@ -15302,7 +15269,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" s="1" t="s">
         <v>813</v>
       </c>
@@ -15310,7 +15277,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" s="1" t="s">
         <v>813</v>
       </c>
@@ -15318,7 +15285,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" s="1" t="s">
         <v>813</v>
       </c>
